--- a/data/trans_orig/P43D-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P43D-Habitat-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64541</t>
+          <t>63934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94030</t>
+          <t>93331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64541</t>
+          <t>63934</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94030</t>
+          <t>93331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91821</t>
+          <t>91307</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124933</t>
+          <t>124453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91821</t>
+          <t>91307</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124933</t>
+          <t>124453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57257</t>
+          <t>56863</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87064</t>
+          <t>87626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57257</t>
+          <t>56863</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87064</t>
+          <t>87626</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44759</t>
+          <t>44656</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72176</t>
+          <t>71289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44759</t>
+          <t>44656</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72176</t>
+          <t>71289</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>107913</t>
+          <t>106891</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>145933</t>
+          <t>146594</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>107913</t>
+          <t>106891</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>145933</t>
+          <t>146594</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134434</t>
+          <t>131221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177109</t>
+          <t>173944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134434</t>
+          <t>131221</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177109</t>
+          <t>173944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111848</t>
+          <t>111880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>151926</t>
+          <t>153196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111848</t>
+          <t>111880</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151926</t>
+          <t>153196</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68365</t>
+          <t>68205</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101749</t>
+          <t>103048</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68365</t>
+          <t>68205</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>101749</t>
+          <t>103048</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76092</t>
+          <t>75927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108779</t>
+          <t>109124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76092</t>
+          <t>75927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108779</t>
+          <t>109124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83541</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>118004</t>
+          <t>116884</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>83541</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118004</t>
+          <t>116884</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100357</t>
+          <t>101103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135839</t>
+          <t>136977</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100357</t>
+          <t>101103</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135839</t>
+          <t>136977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53318</t>
+          <t>53164</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82965</t>
+          <t>82262</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53318</t>
+          <t>53164</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82965</t>
+          <t>82262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>107282</t>
+          <t>108318</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>148638</t>
+          <t>146737</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107282</t>
+          <t>108318</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>148638</t>
+          <t>146737</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169037</t>
+          <t>168194</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>217388</t>
+          <t>215846</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169037</t>
+          <t>168194</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>217388</t>
+          <t>215846</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>130200</t>
+          <t>129668</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>174019</t>
+          <t>174954</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>130200</t>
+          <t>129668</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>174019</t>
+          <t>174954</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104057</t>
+          <t>101981</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>144067</t>
+          <t>143255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104057</t>
+          <t>101981</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>144067</t>
+          <t>143255</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>388118</t>
+          <t>383297</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>459721</t>
+          <t>456740</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>388118</t>
+          <t>383297</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>459721</t>
+          <t>456740</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>515341</t>
+          <t>512955</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>596654</t>
+          <t>594393</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>515341</t>
+          <t>512955</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>596654</t>
+          <t>594393</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>430680</t>
+          <t>434950</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>505487</t>
+          <t>510469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>430680</t>
+          <t>434950</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>505487</t>
+          <t>510469</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>298182</t>
+          <t>299895</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>364568</t>
+          <t>363947</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>298182</t>
+          <t>299895</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>364568</t>
+          <t>363947</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87014</t>
+          <t>86115</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125062</t>
+          <t>122442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87014</t>
+          <t>86115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125062</t>
+          <t>122442</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117325</t>
+          <t>116499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157309</t>
+          <t>155591</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117325</t>
+          <t>116499</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157309</t>
+          <t>155591</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -2970,12 +2970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101600</t>
+          <t>99589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137425</t>
+          <t>139445</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101600</t>
+          <t>99589</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137425</t>
+          <t>139445</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56710</t>
+          <t>58862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91217</t>
+          <t>90348</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56710</t>
+          <t>58862</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91217</t>
+          <t>90348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91311</t>
+          <t>92564</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>133222</t>
+          <t>133202</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91311</t>
+          <t>92564</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133222</t>
+          <t>133202</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -3286,12 +3286,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>227587</t>
+          <t>226250</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>278729</t>
+          <t>275872</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>227587</t>
+          <t>226250</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>278729</t>
+          <t>275872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152091</t>
+          <t>154579</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>200852</t>
+          <t>199471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152091</t>
+          <t>154579</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200852</t>
+          <t>199471</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100470</t>
+          <t>102336</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>142540</t>
+          <t>142813</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100470</t>
+          <t>102336</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>142540</t>
+          <t>142813</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3602,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65168</t>
+          <t>64108</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99498</t>
+          <t>99115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65168</t>
+          <t>64108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99498</t>
+          <t>99115</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149582</t>
+          <t>148811</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>195518</t>
+          <t>194119</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>149582</t>
+          <t>148811</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>195518</t>
+          <t>194119</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -3758,12 +3758,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146404</t>
+          <t>147360</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192457</t>
+          <t>190849</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146404</t>
+          <t>147360</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>192457</t>
+          <t>190849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -3836,12 +3836,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99874</t>
+          <t>97673</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140845</t>
+          <t>140366</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99874</t>
+          <t>97673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>140845</t>
+          <t>140366</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -3996,12 +3996,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>126262</t>
+          <t>128591</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>172035</t>
+          <t>172564</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126262</t>
+          <t>128591</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172035</t>
+          <t>172564</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>206129</t>
+          <t>209534</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256004</t>
+          <t>258686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>206129</t>
+          <t>209534</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256004</t>
+          <t>258686</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -4152,12 +4152,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>151801</t>
+          <t>151991</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>197721</t>
+          <t>199667</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>151801</t>
+          <t>151991</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>197721</t>
+          <t>199667</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -4230,12 +4230,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84455</t>
+          <t>84288</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122279</t>
+          <t>122677</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4265,12 +4265,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84455</t>
+          <t>84288</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>122279</t>
+          <t>122677</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -4390,12 +4390,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>406009</t>
+          <t>409046</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>485969</t>
+          <t>488812</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>406009</t>
+          <t>409046</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>485969</t>
+          <t>488812</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>744514</t>
+          <t>740642</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>840524</t>
+          <t>837069</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>744514</t>
+          <t>740642</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>840524</t>
+          <t>837069</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -4546,12 +4546,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>592669</t>
+          <t>597123</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>681823</t>
+          <t>681811</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>592669</t>
+          <t>597123</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>681823</t>
+          <t>681811</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>380150</t>
+          <t>378136</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>456811</t>
+          <t>454248</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>380150</t>
+          <t>378136</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>456811</t>
+          <t>454248</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69270</t>
+          <t>67141</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>100886</t>
+          <t>100371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69270</t>
+          <t>67141</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>100886</t>
+          <t>100371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -5033,12 +5033,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138247</t>
+          <t>138407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176026</t>
+          <t>177187</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5048,12 +5048,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138247</t>
+          <t>138407</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176026</t>
+          <t>177187</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -5111,12 +5111,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65580</t>
+          <t>63672</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96191</t>
+          <t>95788</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65580</t>
+          <t>63672</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>96191</t>
+          <t>95788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38160</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64720</t>
+          <t>64521</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38160</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64720</t>
+          <t>64521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -5349,12 +5349,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132602</t>
+          <t>132735</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>178090</t>
+          <t>177774</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>132602</t>
+          <t>132735</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178090</t>
+          <t>177774</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>260186</t>
+          <t>261625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>311156</t>
+          <t>313772</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>260186</t>
+          <t>261625</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>311156</t>
+          <t>313772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>47,05%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>132914</t>
+          <t>133003</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>175852</t>
+          <t>176654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132914</t>
+          <t>133003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>175852</t>
+          <t>176654</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -5583,12 +5583,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57648</t>
+          <t>57754</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90332</t>
+          <t>90013</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57648</t>
+          <t>57754</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90332</t>
+          <t>90013</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97811</t>
+          <t>97481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137085</t>
+          <t>138027</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97811</t>
+          <t>97481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137085</t>
+          <t>138027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -5821,12 +5821,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>192838</t>
+          <t>188149</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>236684</t>
+          <t>233277</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>192838</t>
+          <t>188149</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>236684</t>
+          <t>233277</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96568</t>
+          <t>96569</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132384</t>
+          <t>134836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96568</t>
+          <t>96569</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132384</t>
+          <t>134836</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -5977,12 +5977,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47086</t>
+          <t>48852</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78089</t>
+          <t>76420</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47086</t>
+          <t>48852</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78089</t>
+          <t>76420</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -6137,12 +6137,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>152495</t>
+          <t>153379</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>197532</t>
+          <t>198112</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>152495</t>
+          <t>153379</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>197532</t>
+          <t>198112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6187,12 +6187,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -6215,12 +6215,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249939</t>
+          <t>248020</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>302863</t>
+          <t>301518</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6230,12 +6230,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>249939</t>
+          <t>248020</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>302863</t>
+          <t>301518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6265,12 +6265,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125626</t>
+          <t>123064</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>170621</t>
+          <t>168688</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>125626</t>
+          <t>123064</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>170621</t>
+          <t>168688</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6343,12 +6343,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -6371,12 +6371,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78730</t>
+          <t>78016</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>118354</t>
+          <t>115639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78730</t>
+          <t>78016</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118354</t>
+          <t>115639</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -6531,12 +6531,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>491110</t>
+          <t>491489</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>573159</t>
+          <t>571532</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6546,12 +6546,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>491110</t>
+          <t>491489</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>573159</t>
+          <t>571532</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6581,12 +6581,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -6609,12 +6609,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>885927</t>
+          <t>885668</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>978449</t>
+          <t>977905</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>885927</t>
+          <t>885668</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>978449</t>
+          <t>977905</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>454403</t>
+          <t>458077</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>534084</t>
+          <t>537375</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>454403</t>
+          <t>458077</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>534084</t>
+          <t>537375</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -6765,12 +6765,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>250943</t>
+          <t>251512</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>315189</t>
+          <t>311983</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>250943</t>
+          <t>251512</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>315189</t>
+          <t>311983</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -7091,32 +7091,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>85045</t>
+          <t>90722</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73439</t>
+          <t>79478</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96801</t>
+          <t>103123</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7126,32 +7126,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>85045</t>
+          <t>90722</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73439</t>
+          <t>79478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96801</t>
+          <t>103123</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -7169,32 +7169,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95339</t>
+          <t>103325</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83050</t>
+          <t>90586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107803</t>
+          <t>116219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7204,32 +7204,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>95339</t>
+          <t>103325</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83050</t>
+          <t>90586</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107803</t>
+          <t>116219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -7247,32 +7247,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55732</t>
+          <t>58648</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44765</t>
+          <t>47758</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68894</t>
+          <t>71289</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7282,32 +7282,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55732</t>
+          <t>58648</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44765</t>
+          <t>47758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68894</t>
+          <t>71289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -7325,32 +7325,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30667</t>
+          <t>32123</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40958</t>
+          <t>42594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7360,32 +7360,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30667</t>
+          <t>32123</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40958</t>
+          <t>42594</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -7403,17 +7403,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>266782</t>
+          <t>284818</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266782</t>
+          <t>284818</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>266782</t>
+          <t>284818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7438,17 +7438,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>266782</t>
+          <t>284818</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>266782</t>
+          <t>284818</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>266782</t>
+          <t>284818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7485,32 +7485,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>102580</t>
+          <t>112686</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88171</t>
+          <t>97523</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>117435</t>
+          <t>126672</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7520,32 +7520,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>102580</t>
+          <t>112686</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>88171</t>
+          <t>97523</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117435</t>
+          <t>126672</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -7563,32 +7563,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>146663</t>
+          <t>163638</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132542</t>
+          <t>146149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164553</t>
+          <t>180315</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>146663</t>
+          <t>163638</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132542</t>
+          <t>146149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164553</t>
+          <t>180315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -7641,32 +7641,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88287</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75679</t>
+          <t>83730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103124</t>
+          <t>112177</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7676,32 +7676,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88287</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75679</t>
+          <t>83730</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103124</t>
+          <t>112177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -7719,32 +7719,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41509</t>
+          <t>48121</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>37604</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>60335</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7754,32 +7754,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41509</t>
+          <t>48121</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>37604</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>60335</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -7797,17 +7797,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>379039</t>
+          <t>421473</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>379039</t>
+          <t>421473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>379039</t>
+          <t>421473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7832,17 +7832,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>379039</t>
+          <t>421473</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>379039</t>
+          <t>421473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>379039</t>
+          <t>421473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7879,32 +7879,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>129511</t>
+          <t>110915</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100536</t>
+          <t>94853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193803</t>
+          <t>126759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7914,32 +7914,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>129511</t>
+          <t>110915</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100536</t>
+          <t>94853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193803</t>
+          <t>126759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -7957,32 +7957,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104426</t>
+          <t>122030</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74244</t>
+          <t>106446</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>122619</t>
+          <t>138129</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7992,32 +7992,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>104426</t>
+          <t>122030</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74244</t>
+          <t>106446</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>122619</t>
+          <t>138129</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -8035,32 +8035,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>68219</t>
+          <t>78678</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46482</t>
+          <t>65608</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82789</t>
+          <t>92689</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8070,32 +8070,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>68219</t>
+          <t>78678</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46482</t>
+          <t>65608</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82789</t>
+          <t>92689</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -8113,32 +8113,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49983</t>
+          <t>55949</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>45025</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64238</t>
+          <t>71539</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8148,32 +8148,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49983</t>
+          <t>55949</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>45025</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64238</t>
+          <t>71539</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -8191,17 +8191,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>352139</t>
+          <t>367571</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>352139</t>
+          <t>367571</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>352139</t>
+          <t>367571</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8226,17 +8226,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>352139</t>
+          <t>367571</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>352139</t>
+          <t>367571</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>352139</t>
+          <t>367571</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8273,32 +8273,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>221886</t>
+          <t>164198</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>167316</t>
+          <t>147869</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>332329</t>
+          <t>180664</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8308,32 +8308,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>221886</t>
+          <t>164198</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>167316</t>
+          <t>147869</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>332329</t>
+          <t>180664</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -8351,32 +8351,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>151990</t>
+          <t>156938</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>102453</t>
+          <t>140127</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>182169</t>
+          <t>175914</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8386,32 +8386,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>151990</t>
+          <t>156938</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102453</t>
+          <t>140127</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>182169</t>
+          <t>175914</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -8429,32 +8429,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>106151</t>
+          <t>115754</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>70270</t>
+          <t>100173</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>130046</t>
+          <t>133065</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8464,32 +8464,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>106151</t>
+          <t>115754</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70270</t>
+          <t>100173</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>130046</t>
+          <t>133065</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -8507,32 +8507,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>87472</t>
+          <t>93586</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58018</t>
+          <t>79362</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107439</t>
+          <t>110533</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8542,32 +8542,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>87472</t>
+          <t>93586</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58018</t>
+          <t>79362</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107439</t>
+          <t>110533</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -8585,17 +8585,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>567498</t>
+          <t>530476</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>567498</t>
+          <t>530476</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>567498</t>
+          <t>530476</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8620,17 +8620,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>567498</t>
+          <t>530476</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>567498</t>
+          <t>530476</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>567498</t>
+          <t>530476</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8667,32 +8667,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>539022</t>
+          <t>478520</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>466406</t>
+          <t>449858</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>677370</t>
+          <t>513326</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8702,32 +8702,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>539022</t>
+          <t>478520</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>466406</t>
+          <t>449858</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>677370</t>
+          <t>513326</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -8745,32 +8745,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>498418</t>
+          <t>545931</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>433308</t>
+          <t>515344</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>541739</t>
+          <t>578355</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>498418</t>
+          <t>545931</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>433308</t>
+          <t>515344</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>541739</t>
+          <t>578355</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -8823,32 +8823,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>318388</t>
+          <t>350108</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>271802</t>
+          <t>324297</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>351039</t>
+          <t>379849</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8858,32 +8858,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>318388</t>
+          <t>350108</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>271802</t>
+          <t>324297</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>351039</t>
+          <t>379849</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -8901,32 +8901,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>209630</t>
+          <t>229778</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>176144</t>
+          <t>204682</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>237727</t>
+          <t>255878</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8936,32 +8936,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>209630</t>
+          <t>229778</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>176144</t>
+          <t>204682</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>237727</t>
+          <t>255878</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -8979,17 +8979,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9014,17 +9014,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1565458</t>
+          <t>1604338</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
